--- a/dashboard/public/starter-pack/04_Bid_No_Bid_Decision_Toolkit/FLK_04_Competitive_Bid_Analysis.xlsx
+++ b/dashboard/public/starter-pack/04_Bid_No_Bid_Decision_Toolkit/FLK_04_Competitive_Bid_Analysis.xlsx
@@ -7,15 +7,25 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="7500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Setup" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Profiles" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Scoring" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="SWOT" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Summary" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Help" state="visible" r:id="rId10"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId4"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Setup" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Profiles" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Scoring" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="SWOT" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Summary" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Help" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="SetAsideOptions">Lists!$A$2:$A$10</definedName>
+    <definedName name="ContractType">Lists!$B$2:$B$8,Setup!$C$14</definedName>
+    <definedName name="SourceSelection">Lists!$C$2:$C$5</definedName>
+    <definedName name="BusinessSize">Lists!$D$2:$D$9</definedName>
+    <definedName name="YesNoUnknown">Lists!$E$2:$E$4</definedName>
+    <definedName name="RelationshipStrength">Lists!$F$2:$F$5</definedName>
+    <definedName name="PricingApproach">Lists!$G$2:$G$6</definedName>
+    <definedName name="WillTheyBid">Lists!$H$2:$H$6</definedName>
+    <definedName name="ThreatLevel">Lists!$I$2:$I$4</definedName>
     <definedName name="OppName">Setup!$C$5</definedName>
     <definedName name="SolNum">Setup!$C$6</definedName>
     <definedName name="Agency">Setup!$C$7</definedName>
@@ -25,7 +35,6 @@
     <definedName name="YourCo">Setup!$C$11</definedName>
     <definedName name="YourPrice">Setup!$C$12</definedName>
     <definedName name="SetAside">Setup!$C$13</definedName>
-    <definedName name="ContractType">Setup!$C$14</definedName>
     <definedName name="Selection">Setup!$C$15</definedName>
     <definedName name="Incumbent">Setup!$C$16</definedName>
     <definedName name="TotalYou">Scoring!$E$21</definedName>
@@ -40,7 +49,154 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="175">
+  <si>
+    <t>Set-Aside Type</t>
+  </si>
+  <si>
+    <t>Contract Type</t>
+  </si>
+  <si>
+    <t>Source Selection Method</t>
+  </si>
+  <si>
+    <t>Business Size</t>
+  </si>
+  <si>
+    <t>Yes / No / Unknown</t>
+  </si>
+  <si>
+    <t>Relationship Strength</t>
+  </si>
+  <si>
+    <t>Pricing Approach</t>
+  </si>
+  <si>
+    <t>Will They Bid?</t>
+  </si>
+  <si>
+    <t>Threat Level</t>
+  </si>
+  <si>
+    <t>Full and Open</t>
+  </si>
+  <si>
+    <t>FFP — Firm Fixed Price</t>
+  </si>
+  <si>
+    <t>LPTA — Lowest Price Technically Acceptable</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>Aggressive — undercut</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Small Business</t>
+  </si>
+  <si>
+    <t>T&amp;M — Time &amp; Materials</t>
+  </si>
+  <si>
+    <t>Best Value Tradeoff</t>
+  </si>
+  <si>
+    <t>Small</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Some history</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Probably</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>8(a)</t>
+  </si>
+  <si>
+    <t>CPFF — Cost Plus Fixed Fee</t>
+  </si>
+  <si>
+    <t>Highest Technically Rated, Fair &amp; Reasonable</t>
+  </si>
+  <si>
+    <t>Small — 8(a)</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>Unlikely</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>HUBZone</t>
+  </si>
+  <si>
+    <t>CPIF — Cost Plus Incentive</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Small — HUBZone</t>
+  </si>
+  <si>
+    <t>LPTA play</t>
+  </si>
+  <si>
+    <t>SDVOSB</t>
+  </si>
+  <si>
+    <t>IDIQ — Indefinite Delivery</t>
+  </si>
+  <si>
+    <t>Small — SDVOSB</t>
+  </si>
+  <si>
+    <t>WOSB</t>
+  </si>
+  <si>
+    <t>BPA — Blanket Purchase</t>
+  </si>
+  <si>
+    <t>Small — WOSB</t>
+  </si>
+  <si>
+    <t>EDWOSB</t>
+  </si>
+  <si>
+    <t>Small — EDWOSB</t>
+  </si>
+  <si>
+    <t>Total Small Business</t>
+  </si>
   <si>
     <t>COMPETITIVE BID ANALYSIS — HOW TO USE</t>
   </si>
@@ -135,18 +291,9 @@
     <t>e.g. 4200000</t>
   </si>
   <si>
-    <t>Set-Aside Type</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>Contract Type</t>
-  </si>
-  <si>
-    <t>Source Selection Method</t>
-  </si>
-  <si>
     <t>Incumbent on This Contract</t>
   </si>
   <si>
@@ -186,9 +333,6 @@
     <t>UEI / CAGE Code</t>
   </si>
   <si>
-    <t>Business Size</t>
-  </si>
-  <si>
     <t>Revenue (annual est.)</t>
   </si>
   <si>
@@ -229,12 +373,6 @@
   </si>
   <si>
     <t>Likely Pricing Approach</t>
-  </si>
-  <si>
-    <t>Will They Bid?</t>
-  </si>
-  <si>
-    <t>Threat Level</t>
   </si>
   <si>
     <t>Your Edge vs This Competitor</t>
@@ -449,12 +587,21 @@
     <numFmt numFmtId="166" formatCode="+0.00;-0.00;0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -548,6 +695,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF047857"/>
       </patternFill>
     </fill>
@@ -559,11 +711,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -679,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -690,130 +837,136 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1299,6 +1452,211 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="9" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1311,80 +1669,80 @@
   </cols>
   <sheetData>
     <row r="2" ht="38" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="C2"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
+      <c r="B5" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>3</v>
+      <c r="B6" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>4</v>
+      <c r="B8" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>5</v>
+      <c r="B9" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>6</v>
+      <c r="B11" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>7</v>
+      <c r="B12" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>8</v>
+      <c r="B14" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>9</v>
+      <c r="B15" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>10</v>
+      <c r="B17" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18" ht="46" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>11</v>
+      <c r="B18" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="20" ht="70" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>12</v>
+      <c r="B20" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C20"/>
     </row>
@@ -1414,7 +1772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1429,130 +1787,130 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>13</v>
+      <c r="B2" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>14</v>
+      <c r="B3" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8" t="s">
-        <v>16</v>
+      <c r="B5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
-        <v>18</v>
+      <c r="B6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8" t="s">
-        <v>20</v>
+      <c r="B7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
-        <v>22</v>
+      <c r="B8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8" t="s">
-        <v>24</v>
+      <c r="B9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="8" t="s">
-        <v>26</v>
+      <c r="B10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8" t="s">
-        <v>28</v>
+      <c r="B11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="8" t="s">
-        <v>30</v>
+      <c r="B12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8" t="s">
-        <v>32</v>
+      <c r="B13" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8" t="s">
-        <v>32</v>
+      <c r="B14" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8" t="s">
-        <v>32</v>
+      <c r="B15" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8" t="s">
-        <v>36</v>
+      <c r="B16" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>37</v>
+      <c r="B18" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="C18"/>
       <c r="D18"/>
@@ -1565,13 +1923,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick a value" error="Use the dropdown — keeps the rest of the workbook consistent." sqref="C13">
-      <formula1>"Full and Open,Small Business,8(a),HUBZone,SDVOSB,WOSB,EDWOSB,Total Small Business,Other"</formula1>
+      <formula1>SetAsideOptions</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick a value" error="Use the dropdown — keeps the rest of the workbook consistent." sqref="C14">
-      <formula1>"FFP — Firm Fixed Price,T&amp;M — Time &amp; Materials,CPFF — Cost Plus Fixed Fee,CPIF — Cost Plus Incentive,IDIQ — Indefinite Delivery,BPA — Blanket Purchase,Other"</formula1>
+      <formula1>ContractType</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick a value" error="Use the dropdown — keeps the rest of the workbook consistent." sqref="C15">
-      <formula1>"LPTA — Lowest Price Technically Acceptable,Best Value Tradeoff,Highest Technically Rated, Fair &amp; Reasonable,Other"</formula1>
+      <formula1>SourceSelection</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1584,7 +1942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1597,8 +1955,8 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>38</v>
+      <c r="A2" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -1607,8 +1965,8 @@
       <c r="F2"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>39</v>
+      <c r="A3" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -1617,226 +1975,226 @@
       <c r="F3"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>45</v>
+      <c r="A5" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="9">
         <f>IF(YourCo="","(see Setup tab)",YourCo)</f>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="A7" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="A9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="A10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="A11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="A12" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="A17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="A19" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="A21" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="A22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="A23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1856,22 +2214,22 @@
   </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" sqref="B14:F14">
-      <formula1>"Yes,No,Unknown"</formula1>
+      <formula1>YesNoUnknown</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B15:F15">
-      <formula1>"Strong,Some history,Cold,Unknown"</formula1>
+      <formula1>RelationshipStrength</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B22:F22">
-      <formula1>"Aggressive — undercut,Market,Premium,LPTA play,Unknown"</formula1>
+      <formula1>PricingApproach</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B23:F23">
-      <formula1>"Yes,Probably,Unlikely,No,Unknown"</formula1>
+      <formula1>WillTheyBid</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B24:F24">
-      <formula1>"HIGH,MEDIUM,LOW"</formula1>
+      <formula1>ThreatLevel</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B8:F8">
-      <formula1>"Large,Small,Small — 8(a),Small — HUBZone,Small — SDVOSB,Small — WOSB,Small — EDWOSB,Unknown"</formula1>
+      <formula1>BusinessSize</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1884,7 +2242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1899,8 +2257,8 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>66</v>
+      <c r="A2" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -1916,8 +2274,8 @@
       <c r="M2"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>67</v>
+      <c r="A3" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -1933,8 +2291,8 @@
       <c r="M3"/>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>68</v>
+      <c r="A5" s="19" t="s">
+        <v>111</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -1950,458 +2308,458 @@
       <c r="M5"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="18">
+      <c r="A6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="20">
         <f>IF(Profiles!B6="","YOUR CO",Profiles!B6)</f>
       </c>
       <c r="E6"/>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>IF(Profiles!C6="","COMP 1",Profiles!C6)</f>
       </c>
       <c r="G6"/>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>IF(Profiles!D6="","COMP 2",Profiles!D6)</f>
       </c>
       <c r="I6"/>
-      <c r="J6" s="18">
+      <c r="J6" s="20">
         <f>IF(Profiles!E6="","COMP 3",Profiles!E6)</f>
       </c>
       <c r="K6"/>
-      <c r="L6" s="18">
+      <c r="L6" s="20">
         <f>IF(Profiles!F6="","COMP 4",Profiles!F6)</f>
       </c>
       <c r="M6"/>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>74</v>
+      <c r="A7" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
+      <c r="A8" s="21">
         <v>1</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22">
+      <c r="B8" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24">
         <f>IF(OR($C8="",D8=""),"",$C8*D8)</f>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="22">
+      <c r="F8" s="23"/>
+      <c r="G8" s="24">
         <f>IF(OR($C8="",F8=""),"",$C8*F8)</f>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="22">
+      <c r="H8" s="23"/>
+      <c r="I8" s="24">
         <f>IF(OR($C8="",H8=""),"",$C8*H8)</f>
       </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="22">
+      <c r="J8" s="23"/>
+      <c r="K8" s="24">
         <f>IF(OR($C8="",J8=""),"",$C8*J8)</f>
       </c>
-      <c r="L8" s="21"/>
-      <c r="M8" s="22">
+      <c r="L8" s="23"/>
+      <c r="M8" s="24">
         <f>IF(OR($C8="",L8=""),"",$C8*L8)</f>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
+      <c r="A9" s="21">
         <v>2</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22">
+      <c r="B9" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24">
         <f>IF(OR($C9="",D9=""),"",$C9*D9)</f>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="22">
+      <c r="F9" s="23"/>
+      <c r="G9" s="24">
         <f>IF(OR($C9="",F9=""),"",$C9*F9)</f>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="22">
+      <c r="H9" s="23"/>
+      <c r="I9" s="24">
         <f>IF(OR($C9="",H9=""),"",$C9*H9)</f>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="22">
+      <c r="J9" s="23"/>
+      <c r="K9" s="24">
         <f>IF(OR($C9="",J9=""),"",$C9*J9)</f>
       </c>
-      <c r="L9" s="21"/>
-      <c r="M9" s="22">
+      <c r="L9" s="23"/>
+      <c r="M9" s="24">
         <f>IF(OR($C9="",L9=""),"",$C9*L9)</f>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
+      <c r="A10" s="21">
         <v>3</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22">
+      <c r="B10" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="24">
         <f>IF(OR($C10="",D10=""),"",$C10*D10)</f>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="22">
+      <c r="F10" s="23"/>
+      <c r="G10" s="24">
         <f>IF(OR($C10="",F10=""),"",$C10*F10)</f>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="22">
+      <c r="H10" s="23"/>
+      <c r="I10" s="24">
         <f>IF(OR($C10="",H10=""),"",$C10*H10)</f>
       </c>
-      <c r="J10" s="21"/>
-      <c r="K10" s="22">
+      <c r="J10" s="23"/>
+      <c r="K10" s="24">
         <f>IF(OR($C10="",J10=""),"",$C10*J10)</f>
       </c>
-      <c r="L10" s="21"/>
-      <c r="M10" s="22">
+      <c r="L10" s="23"/>
+      <c r="M10" s="24">
         <f>IF(OR($C10="",L10=""),"",$C10*L10)</f>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+      <c r="A11" s="21">
         <v>4</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22">
+      <c r="B11" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24">
         <f>IF(OR($C11="",D11=""),"",$C11*D11)</f>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="22">
+      <c r="F11" s="23"/>
+      <c r="G11" s="24">
         <f>IF(OR($C11="",F11=""),"",$C11*F11)</f>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="22">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24">
         <f>IF(OR($C11="",H11=""),"",$C11*H11)</f>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="22">
+      <c r="J11" s="23"/>
+      <c r="K11" s="24">
         <f>IF(OR($C11="",J11=""),"",$C11*J11)</f>
       </c>
-      <c r="L11" s="21"/>
-      <c r="M11" s="22">
+      <c r="L11" s="23"/>
+      <c r="M11" s="24">
         <f>IF(OR($C11="",L11=""),"",$C11*L11)</f>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+      <c r="A12" s="21">
         <v>5</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22">
+      <c r="B12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24">
         <f>IF(OR($C12="",D12=""),"",$C12*D12)</f>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22">
+      <c r="F12" s="23"/>
+      <c r="G12" s="24">
         <f>IF(OR($C12="",F12=""),"",$C12*F12)</f>
       </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="22">
+      <c r="H12" s="23"/>
+      <c r="I12" s="24">
         <f>IF(OR($C12="",H12=""),"",$C12*H12)</f>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="22">
+      <c r="J12" s="23"/>
+      <c r="K12" s="24">
         <f>IF(OR($C12="",J12=""),"",$C12*J12)</f>
       </c>
-      <c r="L12" s="21"/>
-      <c r="M12" s="22">
+      <c r="L12" s="23"/>
+      <c r="M12" s="24">
         <f>IF(OR($C12="",L12=""),"",$C12*L12)</f>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+      <c r="A13" s="21">
         <v>6</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="22">
+      <c r="B13" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24">
         <f>IF(OR($C13="",D13=""),"",$C13*D13)</f>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22">
+      <c r="F13" s="23"/>
+      <c r="G13" s="24">
         <f>IF(OR($C13="",F13=""),"",$C13*F13)</f>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22">
+      <c r="H13" s="23"/>
+      <c r="I13" s="24">
         <f>IF(OR($C13="",H13=""),"",$C13*H13)</f>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22">
+      <c r="J13" s="23"/>
+      <c r="K13" s="24">
         <f>IF(OR($C13="",J13=""),"",$C13*J13)</f>
       </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="22">
+      <c r="L13" s="23"/>
+      <c r="M13" s="24">
         <f>IF(OR($C13="",L13=""),"",$C13*L13)</f>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
+      <c r="A14" s="21">
         <v>7</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22">
+      <c r="B14" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24">
         <f>IF(OR($C14="",D14=""),"",$C14*D14)</f>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="22">
+      <c r="F14" s="23"/>
+      <c r="G14" s="24">
         <f>IF(OR($C14="",F14=""),"",$C14*F14)</f>
       </c>
-      <c r="H14" s="21"/>
-      <c r="I14" s="22">
+      <c r="H14" s="23"/>
+      <c r="I14" s="24">
         <f>IF(OR($C14="",H14=""),"",$C14*H14)</f>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="22">
+      <c r="J14" s="23"/>
+      <c r="K14" s="24">
         <f>IF(OR($C14="",J14=""),"",$C14*J14)</f>
       </c>
-      <c r="L14" s="21"/>
-      <c r="M14" s="22">
+      <c r="L14" s="23"/>
+      <c r="M14" s="24">
         <f>IF(OR($C14="",L14=""),"",$C14*L14)</f>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
+      <c r="A15" s="21">
         <v>8</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22">
+      <c r="B15" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24">
         <f>IF(OR($C15="",D15=""),"",$C15*D15)</f>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="22">
+      <c r="F15" s="23"/>
+      <c r="G15" s="24">
         <f>IF(OR($C15="",F15=""),"",$C15*F15)</f>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="22">
+      <c r="H15" s="23"/>
+      <c r="I15" s="24">
         <f>IF(OR($C15="",H15=""),"",$C15*H15)</f>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="22">
+      <c r="J15" s="23"/>
+      <c r="K15" s="24">
         <f>IF(OR($C15="",J15=""),"",$C15*J15)</f>
       </c>
-      <c r="L15" s="21"/>
-      <c r="M15" s="22">
+      <c r="L15" s="23"/>
+      <c r="M15" s="24">
         <f>IF(OR($C15="",L15=""),"",$C15*L15)</f>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
+      <c r="A16" s="21">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="22">
+      <c r="B16" s="9"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24">
         <f>IF(OR($C16="",D16=""),"",$C16*D16)</f>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="22">
+      <c r="F16" s="23"/>
+      <c r="G16" s="24">
         <f>IF(OR($C16="",F16=""),"",$C16*F16)</f>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="22">
+      <c r="H16" s="23"/>
+      <c r="I16" s="24">
         <f>IF(OR($C16="",H16=""),"",$C16*H16)</f>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22">
+      <c r="J16" s="23"/>
+      <c r="K16" s="24">
         <f>IF(OR($C16="",J16=""),"",$C16*J16)</f>
       </c>
-      <c r="L16" s="21"/>
-      <c r="M16" s="22">
+      <c r="L16" s="23"/>
+      <c r="M16" s="24">
         <f>IF(OR($C16="",L16=""),"",$C16*L16)</f>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
+      <c r="A17" s="21">
         <v>10</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22">
+      <c r="B17" s="9"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24">
         <f>IF(OR($C17="",D17=""),"",$C17*D17)</f>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="22">
+      <c r="F17" s="23"/>
+      <c r="G17" s="24">
         <f>IF(OR($C17="",F17=""),"",$C17*F17)</f>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="22">
+      <c r="H17" s="23"/>
+      <c r="I17" s="24">
         <f>IF(OR($C17="",H17=""),"",$C17*H17)</f>
       </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="22">
+      <c r="J17" s="23"/>
+      <c r="K17" s="24">
         <f>IF(OR($C17="",J17=""),"",$C17*J17)</f>
       </c>
-      <c r="L17" s="21"/>
-      <c r="M17" s="22">
+      <c r="L17" s="23"/>
+      <c r="M17" s="24">
         <f>IF(OR($C17="",L17=""),"",$C17*L17)</f>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
+      <c r="A18" s="21">
         <v>11</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="22">
+      <c r="B18" s="9"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24">
         <f>IF(OR($C18="",D18=""),"",$C18*D18)</f>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="22">
+      <c r="F18" s="23"/>
+      <c r="G18" s="24">
         <f>IF(OR($C18="",F18=""),"",$C18*F18)</f>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22">
+      <c r="H18" s="23"/>
+      <c r="I18" s="24">
         <f>IF(OR($C18="",H18=""),"",$C18*H18)</f>
       </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="22">
+      <c r="J18" s="23"/>
+      <c r="K18" s="24">
         <f>IF(OR($C18="",J18=""),"",$C18*J18)</f>
       </c>
-      <c r="L18" s="21"/>
-      <c r="M18" s="22">
+      <c r="L18" s="23"/>
+      <c r="M18" s="24">
         <f>IF(OR($C18="",L18=""),"",$C18*L18)</f>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
+      <c r="A19" s="21">
         <v>12</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="22">
+      <c r="B19" s="9"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24">
         <f>IF(OR($C19="",D19=""),"",$C19*D19)</f>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22">
+      <c r="F19" s="23"/>
+      <c r="G19" s="24">
         <f>IF(OR($C19="",F19=""),"",$C19*F19)</f>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="22">
+      <c r="H19" s="23"/>
+      <c r="I19" s="24">
         <f>IF(OR($C19="",H19=""),"",$C19*H19)</f>
       </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="22">
+      <c r="J19" s="23"/>
+      <c r="K19" s="24">
         <f>IF(OR($C19="",J19=""),"",$C19*J19)</f>
       </c>
-      <c r="L19" s="21"/>
-      <c r="M19" s="22">
+      <c r="L19" s="23"/>
+      <c r="M19" s="24">
         <f>IF(OR($C19="",L19=""),"",$C19*L19)</f>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>83</v>
+      <c r="A21" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="B21"/>
-      <c r="C21" s="23">
+      <c r="C21" s="25">
         <f>SUM(C8:C19)</f>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="25">
+      <c r="D21" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="27">
         <f>IFERROR(SUM(E8:E19),0)</f>
       </c>
-      <c r="F21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="25">
+      <c r="F21" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="27">
         <f>IFERROR(SUM(G8:G19),0)</f>
       </c>
-      <c r="H21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="25">
+      <c r="H21" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="27">
         <f>IFERROR(SUM(I8:I19),0)</f>
       </c>
-      <c r="J21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="K21" s="25">
+      <c r="J21" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="K21" s="27">
         <f>IFERROR(SUM(K8:K19),0)</f>
       </c>
-      <c r="L21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="M21" s="25">
+      <c r="L21" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="M21" s="27">
         <f>IFERROR(SUM(M8:M19),0)</f>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>85</v>
+      <c r="A22" s="28" t="s">
+        <v>128</v>
       </c>
       <c r="B22"/>
-      <c r="D22" s="27">
+      <c r="D22" s="29">
         <f>IF(ROUND(WeightTotal,4)=1,"OK — weights sum to 100%","WARNING — weights sum to " &amp; TEXT(WeightTotal,"0%") &amp; ". Fix before reading Summary.")</f>
       </c>
       <c r="E22"/>
@@ -2497,7 +2855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2510,197 +2868,197 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>86</v>
+      <c r="A2" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>87</v>
+      <c r="A3" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="15">
         <f>IF(Profiles!C6="","COMPETITOR 1",Profiles!C6)</f>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <f>IF(Profiles!D6="","COMPETITOR 2",Profiles!D6)</f>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>88</v>
+      <c r="A6" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="B6"/>
       <c r="C6"/>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
+      <c r="A7" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="A8" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="A9" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+      <c r="A10" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
+      <c r="A11" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
-        <v>94</v>
+      <c r="A13" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
+      <c r="A14" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
-        <v>95</v>
+      <c r="A20" s="34" t="s">
+        <v>138</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
     </row>
     <row r="21" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
+      <c r="A25" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
-        <v>96</v>
+      <c r="A27" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
     </row>
     <row r="28" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
+      <c r="A28" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+      <c r="A29" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
+      <c r="A30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
+      <c r="A31" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
+      <c r="A32" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2721,7 +3079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2734,8 +3092,8 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>97</v>
+      <c r="A2" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -2744,7 +3102,7 @@
       <c r="F2"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <f>IF(OppName="","Add opportunity details on the Setup tab to see this populate.","Opportunity: " &amp; OppName &amp; "   ·   Sol# " &amp; SolNum &amp; "   ·   Due " &amp; IF(DueDate="","TBD",TEXT(DueDate,"yyyy-mm-dd")))</f>
       </c>
       <c r="B3"/>
@@ -2754,128 +3112,128 @@
       <c r="F3"/>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>103</v>
+      <c r="A5" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="8">
         <f>IF(Profiles!B6="","YOUR COMPANY",Profiles!B6)</f>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="38">
         <f>TotalYou</f>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>104</v>
+      <c r="C6" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="8">
         <f>IF(Profiles!C6="","COMPETITOR 1",Profiles!C6)</f>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="38">
         <f>TotalC1</f>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="41">
         <f>TotalYou - TotalC1</f>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="40">
         <f>IF(Profiles!C23="","-",Profiles!C23)</f>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="42">
         <f>IF(Profiles!C24="","-",Profiles!C24)</f>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <f>IF(Profiles!C25="","(add edge note in Profiles)",Profiles!C25)</f>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="8">
         <f>IF(Profiles!D6="","COMPETITOR 2",Profiles!D6)</f>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="38">
         <f>TotalC2</f>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="41">
         <f>TotalYou - TotalC2</f>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="40">
         <f>IF(Profiles!D23="","-",Profiles!D23)</f>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="42">
         <f>IF(Profiles!D24="","-",Profiles!D24)</f>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="9">
         <f>IF(Profiles!D25="","(add edge note in Profiles)",Profiles!D25)</f>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="8">
         <f>IF(Profiles!E6="","COMPETITOR 3",Profiles!E6)</f>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="38">
         <f>TotalC3</f>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="41">
         <f>TotalYou - TotalC3</f>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="40">
         <f>IF(Profiles!E23="","-",Profiles!E23)</f>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="42">
         <f>IF(Profiles!E24="","-",Profiles!E24)</f>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="9">
         <f>IF(Profiles!E25="","(add edge note in Profiles)",Profiles!E25)</f>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="8">
         <f>IF(Profiles!F6="","COMPETITOR 4",Profiles!F6)</f>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="38">
         <f>TotalC4</f>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="41">
         <f>TotalYou - TotalC4</f>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="40">
         <f>IF(Profiles!F23="","-",Profiles!F23)</f>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="42">
         <f>IF(Profiles!F24="","-",Profiles!F24)</f>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="9">
         <f>IF(Profiles!F25="","(add edge note in Profiles)",Profiles!F25)</f>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>105</v>
+      <c r="A12" s="14" t="s">
+        <v>148</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -2884,32 +3242,32 @@
       <c r="F12"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="22">
+      <c r="A13" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="24">
         <f>MAX(TotalC1,TotalC2,TotalC3,TotalC4)</f>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="39">
+      <c r="A14" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="41">
         <f>TotalYou - MAX(TotalC1,TotalC2,TotalC3,TotalC4)</f>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="41">
+      <c r="A15" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="43">
         <f>IF(OR(TotalYou=0,MAX(TotalC1,TotalC2,TotalC3,TotalC4)=0),"Fill Scoring tab first",ROUND(MAX(0.05,MIN(0.95,0.5+(TotalYou-MAX(TotalC1,TotalC2,TotalC3,TotalC4))/(2*MAX(TotalYou,MAX(TotalC1,TotalC2,TotalC3,TotalC4))))),2))</f>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>109</v>
+      <c r="A17" s="14" t="s">
+        <v>152</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -2918,18 +3276,18 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="42">
+      <c r="A18" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="44">
         <f>IF(OR(YourPrice="",OppValue="",OppValue=0),"Add prices on Setup tab",YourPrice/OppValue)</f>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="43">
+      <c r="A19" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" s="45">
         <f>IF(OR(YourPrice="",OppValue="",OppValue=0),"-",IF(YourPrice/OppValue&lt;0.9,"Aggressive — verify margins hold",IF(YourPrice/OppValue&lt;1.05,"Market — defendable","Premium — needs strong technical story")))</f>
       </c>
       <c r="C19"/>
@@ -2938,8 +3296,8 @@
       <c r="F19"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>112</v>
+      <c r="A21" s="14" t="s">
+        <v>155</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
@@ -2948,7 +3306,7 @@
       <c r="F21"/>
     </row>
     <row r="22" ht="60" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="44">
+      <c r="A22" s="46">
         <f>IF(OR(TotalYou=0,MAX(TotalC1,TotalC2,TotalC3,TotalC4)=0),"Fill the Scoring tab — recommendation pending.",IF(TotalYou-MAX(TotalC1,TotalC2,TotalC3,TotalC4)&gt;=1,"BID. You lead the field on weighted score. Lock the win themes on your top three factors and protect against price erosion.",IF(TotalYou-MAX(TotalC1,TotalC2,TotalC3,TotalC4)&gt;=-0.5,"BID WITH CAUTION. Race is close. Identify the two factors with the largest competitor lead and rework your approach before the proposal start.",IF(TotalYou-MAX(TotalC1,TotalC2,TotalC3,TotalC4)&gt;=-1.5,"NO-BID CANDIDATE. Multiple competitors out-score you on weighted factors. Either find a teaming partner who closes the gap, or save the proposal budget for a better fit.","NO-BID. The field is well ahead. Use this opportunity to learn — request a debrief if it lands, and add the winners to your competitor watchlist."))))</f>
       </c>
       <c r="B22"/>
@@ -2958,8 +3316,8 @@
       <c r="F22"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="45" t="s">
-        <v>113</v>
+      <c r="A24" s="47" t="s">
+        <v>156</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
@@ -3019,7 +3377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3033,110 +3391,110 @@
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>114</v>
+      <c r="B2" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="C2"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>115</v>
+      <c r="B3" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
-        <v>116</v>
+      <c r="B5" s="34" t="s">
+        <v>159</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>117</v>
+      <c r="B6" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="s">
-        <v>118</v>
+      <c r="B8" s="34" t="s">
+        <v>161</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
-        <v>119</v>
+      <c r="B9" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="32" t="s">
-        <v>120</v>
+      <c r="B11" s="34" t="s">
+        <v>163</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>121</v>
+      <c r="B12" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="32" t="s">
-        <v>122</v>
+      <c r="B14" s="34" t="s">
+        <v>165</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>123</v>
+      <c r="B15" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="32" t="s">
-        <v>124</v>
+      <c r="B17" s="34" t="s">
+        <v>167</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>125</v>
+      <c r="B18" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="20" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="32" t="s">
-        <v>126</v>
+      <c r="B20" s="34" t="s">
+        <v>169</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>127</v>
+      <c r="B21" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="23" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="32" t="s">
-        <v>128</v>
+      <c r="B23" s="34" t="s">
+        <v>171</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>129</v>
+      <c r="B24" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="26" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="32" t="s">
-        <v>130</v>
+      <c r="B26" s="34" t="s">
+        <v>173</v>
       </c>
       <c r="C26"/>
     </row>
     <row r="27" ht="60" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>131</v>
+      <c r="B27" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="C27"/>
     </row>
